--- a/dataset comparison.xlsx
+++ b/dataset comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kushn\projects\kaggle\customer churn\Telco customer churn 11.1.3\notebooks\telco-customer-churn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56986B8-F624-4B07-979B-E7AEDE93509C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB49246A-7F0F-49DE-B498-ED0375ED5BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/dataset comparison.xlsx
+++ b/dataset comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kushn\projects\kaggle\customer churn\Telco customer churn 11.1.3\notebooks\telco-customer-churn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB49246A-7F0F-49DE-B498-ED0375ED5BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDD42AB-2B8D-493A-B09F-EFEC962375AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1125,18 +1125,18 @@
       <c r="B46" t="s">
         <v>63</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" t="s">
         <v>54</v>
       </c>
     </row>
